--- a/iC_LNG_NQI/РЕГИСТРЫ.xlsx
+++ b/iC_LNG_NQI/РЕГИСТРЫ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agest\Downloads\Telegram Desktop\iC_LNG_NQI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB5F30C-B162-40B1-A994-1B19D8C0C3D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C24DBF4-804A-4007-83B4-B26CFB2AC5E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,16 +328,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -354,6 +345,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,47 +641,47 @@
   <cols>
     <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
     <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="25.109375" customWidth="1"/>
     <col min="12" max="13" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="14" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="10"/>
+      <c r="K1" s="8"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -694,7 +694,7 @@
       <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -703,22 +703,22 @@
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="14">
         <v>176</v>
       </c>
       <c r="I2" s="2">
         <v>10110000</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="10"/>
+      <c r="K2" s="8"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
@@ -731,29 +731,29 @@
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9"/>
+      <c r="C3" s="15"/>
       <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="14">
         <v>166</v>
       </c>
       <c r="I3" s="2">
         <v>10100110</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="8"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -766,29 +766,29 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="14">
         <v>245</v>
       </c>
       <c r="I4" s="2">
         <v>11110101</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="10"/>
+      <c r="K4" s="8"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -801,29 +801,29 @@
       <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="15"/>
       <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="14">
         <v>138</v>
       </c>
       <c r="I5" s="2">
         <v>10001010</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="10"/>
+      <c r="K5" s="8"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -836,29 +836,29 @@
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="15"/>
       <c r="D6" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>207</v>
       </c>
       <c r="I6" s="2">
         <v>11001111</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="10"/>
+      <c r="K6" s="8"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -871,29 +871,29 @@
       <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="15"/>
       <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="9" t="s">
         <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>173</v>
       </c>
       <c r="I7" s="2">
         <v>10101101</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="10"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -915,14 +915,14 @@
       <c r="E8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -935,7 +935,7 @@
       <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="16" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -944,16 +944,16 @@
       <c r="E9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="10"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="8"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -966,17 +966,17 @@
       <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="8"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -989,7 +989,7 @@
       <c r="B11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -998,16 +998,16 @@
       <c r="E11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="10"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="8"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1020,21 +1020,21 @@
       <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="8"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -1047,21 +1047,21 @@
       <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="8"/>
+      <c r="C13" s="16"/>
       <c r="D13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1074,21 +1074,21 @@
       <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -1101,21 +1101,21 @@
       <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="8"/>
+      <c r="C15" s="16"/>
       <c r="D15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -1128,21 +1128,21 @@
       <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -1155,40 +1155,40 @@
       <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="8"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
     <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -1203,28 +1203,28 @@
       <c r="F19" s="6"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
@@ -1585,13 +1585,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G11:J11"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="C11:C17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G11:J11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
